--- a/0 zombie type/sun/sun_info.xlsx
+++ b/0 zombie type/sun/sun_info.xlsx
@@ -7,7 +7,8 @@
     <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
-    <sheet name="main" sheetId="5" r:id="rId1"/>
+    <sheet name="NE1" sheetId="6" r:id="rId1"/>
+    <sheet name="N6E1.5 68" sheetId="5" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="34">
   <si>
     <t>地图类型</t>
   </si>
@@ -68,64 +69,67 @@
     <t>用户ID</t>
   </si>
   <si>
+    <t>白眼</t>
+  </si>
+  <si>
+    <t>模式ID</t>
+  </si>
+  <si>
+    <t>密度</t>
+  </si>
+  <si>
+    <t>已完成f数（偶数）</t>
+  </si>
+  <si>
+    <t>冲关选卡数</t>
+  </si>
+  <si>
+    <t>舞王</t>
+  </si>
+  <si>
+    <t>阳光初值</t>
+  </si>
+  <si>
+    <t>破阵阳光值</t>
+  </si>
+  <si>
+    <t>阳光无上限</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>计算模式</t>
+  </si>
+  <si>
+    <t>1-随机种子模拟</t>
+  </si>
+  <si>
+    <t>模式1</t>
+  </si>
+  <si>
+    <t>模拟次数</t>
+  </si>
+  <si>
+    <t>输出种子数</t>
+  </si>
+  <si>
+    <t>模式2</t>
+  </si>
+  <si>
+    <t>种子</t>
+  </si>
+  <si>
+    <t>6A25E7B6</t>
+  </si>
+  <si>
     <t>气球</t>
   </si>
   <si>
-    <t>模式ID</t>
-  </si>
-  <si>
-    <t>舞王</t>
-  </si>
-  <si>
-    <t>已完成f数（偶数）</t>
-  </si>
-  <si>
-    <t>白眼</t>
-  </si>
-  <si>
-    <t>冲关选卡数</t>
-  </si>
-  <si>
     <t>撑杆</t>
   </si>
   <si>
-    <t>阳光初值</t>
-  </si>
-  <si>
-    <t>密度</t>
-  </si>
-  <si>
-    <t>破阵阳光值</t>
-  </si>
-  <si>
-    <t>阳光无上限</t>
-  </si>
-  <si>
     <t>是</t>
-  </si>
-  <si>
-    <t>计算模式</t>
-  </si>
-  <si>
-    <t>1-随机种子模拟</t>
-  </si>
-  <si>
-    <t>模式1</t>
-  </si>
-  <si>
-    <t>模拟次数</t>
-  </si>
-  <si>
-    <t>输出种子数</t>
-  </si>
-  <si>
-    <t>模式2</t>
-  </si>
-  <si>
-    <t>种子</t>
-  </si>
-  <si>
-    <t>6A25E7B6</t>
   </si>
 </sst>
 </file>
@@ -1278,6 +1282,334 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr defaultColWidth="9.16346153846154" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="29.6923076923077" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.1538461538462" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.16346153846154" style="1"/>
+    <col min="4" max="5" width="7" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.69230769230769" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.16346153846154" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="4:6">
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3">
+        <v>43.8763</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3">
+        <v>10000</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3">
+        <v>-295.3125</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="4:6">
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="3">
+        <v>-359.375</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="3">
+        <v>54.6875</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3">
+        <v>13</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="3">
+        <v>-76.5625</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2000</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="3">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="3">
+        <v>5000</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="3">
+        <v>-76.5625</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="3">
+        <v>10000</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-56.25</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="3">
+        <v>-500</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="3">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:6">
+      <c r="A12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="4:6">
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:6">
+      <c r="A14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="4:6">
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:6">
+      <c r="A16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:6">
+      <c r="A17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="3">
+        <v>10000</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:6">
+      <c r="A18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="3">
+        <v>10</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="4:6">
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:6">
+      <c r="A20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:6">
+      <c r="A21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:6">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:6">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:6">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="4:6">
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A20:B20"/>
+  </mergeCells>
+  <dataValidations count="6">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1 A4:B4 A6 B17 B21 B6:B10 F3:F25"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
+      <formula1>"DE/MGE/AQE,NE,PE/FE,RE/ME"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3">
+      <formula1>"1/-1,1/0"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E11 D9:D11 E9:E10 D12:E25 D3:E8">
+      <formula1>"空,路障,撑杆,铁桶,读报,铁门,橄榄,舞王,潜水,冰车,海豚,小丑,气球,矿工,跳跳,蹦极,扶梯,投篮,白眼,红眼,密度"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12">
+      <formula1>"否,是"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B14">
+      <formula1>"1-随机种子模拟,2-固定种子模拟"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:F25"/>
   <sheetFormatPr defaultColWidth="9.16346153846154" defaultRowHeight="16.8" outlineLevelCol="5"/>
@@ -1367,7 +1699,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>8</v>
@@ -1384,7 +1716,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>8</v>
@@ -1401,7 +1733,7 @@
         <v>2000</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>8</v>
@@ -1412,13 +1744,13 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="3">
         <v>500000</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>8</v>
@@ -1429,13 +1761,13 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="3">
         <v>10000</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>8</v>
@@ -1446,7 +1778,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" s="3">
         <v>-500</v>
@@ -1455,7 +1787,7 @@
         <v>11</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F11" s="3">
         <v>60.15625</v>
@@ -1463,16 +1795,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F12" s="3">
         <v>-52.34375</v>
@@ -1485,10 +1817,10 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -1501,7 +1833,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" s="2"/>
       <c r="D16" s="3"/>
@@ -1510,7 +1842,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B17" s="3">
         <v>100</v>
@@ -1521,7 +1853,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B18" s="3">
         <v>10</v>
@@ -1537,7 +1869,7 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B20" s="2"/>
       <c r="D20" s="3"/>
@@ -1546,10 +1878,10 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -1588,15 +1920,12 @@
     <mergeCell ref="A20:B20"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1 F3 A4 B4 F4 A6 B6 B7 B8 B9 B10 B17 B21 F5:F25"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1 A4:B4 A6 B17 B21 B6:B10 F3:F25"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
       <formula1>"DE/MGE/AQE,NE,PE/FE,RE/ME"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3">
       <formula1>"1/-1,1/0"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3 D4 D5:D25 E3:E10 E11:E25">
-      <formula1>"空,路障,撑杆,铁桶,读报,铁门,橄榄,舞王,潜水,冰车,海豚,小丑,气球,矿工,跳跳,蹦极,扶梯,投篮,白眼,红眼,密度"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12">
       <formula1>"否,是"</formula1>
@@ -1604,6 +1933,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B14">
       <formula1>"1-随机种子模拟,2-固定种子模拟"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:E25">
+      <formula1>"空,路障,撑杆,铁桶,读报,铁门,橄榄,舞王,潜水,冰车,海豚,小丑,气球,矿工,跳跳,蹦极,扶梯,投篮,白眼,红眼,密度"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/0 zombie type/sun/sun_info.xlsx
+++ b/0 zombie type/sun/sun_info.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="18855" windowHeight="9270"/>
   </bookViews>
   <sheets>
-    <sheet name="NE1" sheetId="6" r:id="rId1"/>
-    <sheet name="N6E1.5 68" sheetId="5" r:id="rId2"/>
+    <sheet name="DE 0.5 hqyx" sheetId="7" r:id="rId1"/>
+    <sheet name="NE1" sheetId="6" r:id="rId2"/>
+    <sheet name="N6E1.5 68" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,102 +29,108 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="36">
   <si>
     <t>地图类型</t>
   </si>
   <si>
+    <t>DE/MGE/AQE</t>
+  </si>
+  <si>
+    <t>阳光模型</t>
+  </si>
+  <si>
+    <t>因子1</t>
+  </si>
+  <si>
+    <t>因子2</t>
+  </si>
+  <si>
+    <t>系数</t>
+  </si>
+  <si>
+    <t>变量取值</t>
+  </si>
+  <si>
+    <t>1/-1</t>
+  </si>
+  <si>
+    <t>空</t>
+  </si>
+  <si>
+    <t>密度的通常波权重和阈值线</t>
+  </si>
+  <si>
+    <t>红眼</t>
+  </si>
+  <si>
+    <t>橄榄</t>
+  </si>
+  <si>
+    <t>用户ID</t>
+  </si>
+  <si>
+    <t>冰车</t>
+  </si>
+  <si>
+    <t>模式ID</t>
+  </si>
+  <si>
+    <t>气球</t>
+  </si>
+  <si>
+    <t>已完成f数（偶数）</t>
+  </si>
+  <si>
+    <t>舞王</t>
+  </si>
+  <si>
+    <t>冲关选卡数</t>
+  </si>
+  <si>
+    <t>白眼</t>
+  </si>
+  <si>
+    <t>阳光初值</t>
+  </si>
+  <si>
+    <t>密度</t>
+  </si>
+  <si>
+    <t>破阵阳光值</t>
+  </si>
+  <si>
+    <t>阳光无上限</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>计算模式</t>
+  </si>
+  <si>
+    <t>1-随机种子模拟</t>
+  </si>
+  <si>
+    <t>模式1</t>
+  </si>
+  <si>
+    <t>模拟次数</t>
+  </si>
+  <si>
+    <t>输出种子数</t>
+  </si>
+  <si>
+    <t>模式2</t>
+  </si>
+  <si>
+    <t>种子</t>
+  </si>
+  <si>
+    <t>6A25E7B6</t>
+  </si>
+  <si>
     <t>NE</t>
-  </si>
-  <si>
-    <t>阳光模型</t>
-  </si>
-  <si>
-    <t>因子1</t>
-  </si>
-  <si>
-    <t>因子2</t>
-  </si>
-  <si>
-    <t>系数</t>
-  </si>
-  <si>
-    <t>变量取值</t>
-  </si>
-  <si>
-    <t>1/-1</t>
-  </si>
-  <si>
-    <t>空</t>
-  </si>
-  <si>
-    <t>密度的通常波权重和阈值线</t>
-  </si>
-  <si>
-    <t>红眼</t>
-  </si>
-  <si>
-    <t>橄榄</t>
-  </si>
-  <si>
-    <t>用户ID</t>
-  </si>
-  <si>
-    <t>白眼</t>
-  </si>
-  <si>
-    <t>模式ID</t>
-  </si>
-  <si>
-    <t>密度</t>
-  </si>
-  <si>
-    <t>已完成f数（偶数）</t>
-  </si>
-  <si>
-    <t>冲关选卡数</t>
-  </si>
-  <si>
-    <t>舞王</t>
-  </si>
-  <si>
-    <t>阳光初值</t>
-  </si>
-  <si>
-    <t>破阵阳光值</t>
-  </si>
-  <si>
-    <t>阳光无上限</t>
-  </si>
-  <si>
-    <t>否</t>
-  </si>
-  <si>
-    <t>计算模式</t>
-  </si>
-  <si>
-    <t>1-随机种子模拟</t>
-  </si>
-  <si>
-    <t>模式1</t>
-  </si>
-  <si>
-    <t>模拟次数</t>
-  </si>
-  <si>
-    <t>输出种子数</t>
-  </si>
-  <si>
-    <t>模式2</t>
-  </si>
-  <si>
-    <t>种子</t>
-  </si>
-  <si>
-    <t>6A25E7B6</t>
-  </si>
-  <si>
-    <t>气球</t>
   </si>
   <si>
     <t>撑杆</t>
@@ -1284,14 +1291,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultColWidth="9.16346153846154" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="29.6923076923077" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.1538461538462" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.16346153846154" style="1"/>
+    <col min="1" max="1" width="29.6916666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.16666666666667" style="1"/>
     <col min="4" max="5" width="7" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.69230769230769" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.16346153846154" style="1"/>
+    <col min="6" max="6" width="9.69166666666667" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.16666666666667" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -1307,7 +1314,7 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="4:6">
+    <row r="2" s="1" customFormat="1" spans="1:6">
       <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1332,7 +1339,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="3">
-        <v>43.8763</v>
+        <v>232.452119</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:6">
@@ -1340,7 +1347,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="3">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>10</v>
@@ -1349,10 +1356,10 @@
         <v>8</v>
       </c>
       <c r="F4" s="3">
-        <v>-295.3125</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="4:6">
+        <v>-121.027542</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:6">
       <c r="D5" s="3" t="s">
         <v>11</v>
       </c>
@@ -1360,7 +1367,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="3">
-        <v>-359.375</v>
+        <v>-339.777542</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:6">
@@ -1377,7 +1384,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="3">
-        <v>54.6875</v>
+        <v>-323.622881</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:6">
@@ -1394,7 +1401,7 @@
         <v>8</v>
       </c>
       <c r="F7" s="3">
-        <v>-76.5625</v>
+        <v>-439.247881</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:6">
@@ -1405,101 +1412,125 @@
         <v>2000</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F8" s="3">
-        <v>-50</v>
+        <v>-241.340042</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="3">
         <v>5000</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F9" s="3">
-        <v>-76.5625</v>
+        <v>202.409958</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" s="3">
         <v>10000</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F10" s="3">
-        <v>-56.25</v>
+        <v>-113.983051</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B11" s="3">
         <v>-500</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F11" s="3">
-        <v>-50</v>
+        <v>-137.685381</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="4:6">
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="3">
+        <v>-134.560381</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:6">
+      <c r="D13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="3">
+        <v>-246.027542</v>
+      </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:6">
       <c r="A14" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="4:6">
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-143.220339</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:6">
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3">
+        <v>-100</v>
+      </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B16" s="2"/>
       <c r="D16" s="3"/>
@@ -1508,7 +1539,7 @@
     </row>
     <row r="17" s="1" customFormat="1" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B17" s="3">
         <v>10000</v>
@@ -1519,7 +1550,7 @@
     </row>
     <row r="18" s="1" customFormat="1" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B18" s="3">
         <v>10</v>
@@ -1528,14 +1559,14 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" s="1" customFormat="1" spans="4:6">
+    <row r="19" s="1" customFormat="1" spans="1:6">
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B20" s="2"/>
       <c r="D20" s="3"/>
@@ -1544,10 +1575,10 @@
     </row>
     <row r="21" s="1" customFormat="1" spans="1:6">
       <c r="A21" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -1574,7 +1605,335 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" s="1" customFormat="1" spans="4:6">
+    <row r="25" s="1" customFormat="1" spans="1:6">
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A20:B20"/>
+  </mergeCells>
+  <dataValidations count="6">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1 A4:B4 A6 F15 B17 B21 B6:B10 F3:F14 F16:F25"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
+      <formula1>"DE/MGE/AQE,NE,PE/FE,RE/ME"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3">
+      <formula1>"1/-1,1/0"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12">
+      <formula1>"否,是"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B14">
+      <formula1>"1-随机种子模拟,2-固定种子模拟"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D15:E15 D12:E14 D3:E11 D16:E25">
+      <formula1>"空,路障,撑杆,铁桶,读报,铁门,橄榄,舞王,潜水,冰车,海豚,小丑,气球,矿工,跳跳,蹦极,扶梯,投篮,白眼,红眼,密度"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="29.6916666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.16666666666667" style="1"/>
+    <col min="4" max="5" width="7" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.69166666666667" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.16666666666667" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:6">
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3">
+        <v>43.8763</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3">
+        <v>10000</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3">
+        <v>-295.3125</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:6">
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="3">
+        <v>-359.375</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="3">
+        <v>54.6875</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3">
+        <v>13</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="3">
+        <v>-76.5625</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2000</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="3">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="3">
+        <v>5000</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="3">
+        <v>-76.5625</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="3">
+        <v>10000</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-56.25</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="3">
+        <v>-500</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="3">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:6">
+      <c r="A12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:6">
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:6">
+      <c r="A14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:6">
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:6">
+      <c r="A16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:6">
+      <c r="A17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="3">
+        <v>10000</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:6">
+      <c r="A18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="3">
+        <v>10</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:6">
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:6">
+      <c r="A20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:6">
+      <c r="A21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:6">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:6">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:6">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:6">
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -1593,14 +1952,14 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3">
       <formula1>"1/-1,1/0"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E11 D9:D11 E9:E10 D12:E25 D3:E8">
-      <formula1>"空,路障,撑杆,铁桶,读报,铁门,橄榄,舞王,潜水,冰车,海豚,小丑,气球,矿工,跳跳,蹦极,扶梯,投篮,白眼,红眼,密度"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12">
       <formula1>"否,是"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B14">
       <formula1>"1-随机种子模拟,2-固定种子模拟"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:E25">
+      <formula1>"空,路障,撑杆,铁桶,读报,铁门,橄榄,舞王,潜水,冰车,海豚,小丑,气球,矿工,跳跳,蹦极,扶梯,投篮,白眼,红眼,密度"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1608,18 +1967,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultColWidth="9.16346153846154" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="29.6923076923077" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.1538461538462" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.16346153846154" style="1"/>
+    <col min="1" max="1" width="29.6916666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.16666666666667" style="1"/>
     <col min="4" max="5" width="7" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.69230769230769" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.16346153846154" style="1"/>
+    <col min="6" max="6" width="9.69166666666667" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.16666666666667" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1627,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -1635,7 +1994,7 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="4:6">
+    <row r="2" spans="1:6">
       <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1680,7 +2039,7 @@
         <v>-38.28125</v>
       </c>
     </row>
-    <row r="5" spans="4:6">
+    <row r="5" spans="1:6">
       <c r="D5" s="3" t="s">
         <v>11</v>
       </c>
@@ -1699,7 +2058,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>8</v>
@@ -1716,7 +2075,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>8</v>
@@ -1733,7 +2092,7 @@
         <v>2000</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>8</v>
@@ -1744,13 +2103,13 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="3">
         <v>500000</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>8</v>
@@ -1761,13 +2120,13 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" s="3">
         <v>10000</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>8</v>
@@ -1778,7 +2137,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B11" s="3">
         <v>-500</v>
@@ -1787,7 +2146,7 @@
         <v>11</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F11" s="3">
         <v>60.15625</v>
@@ -1795,45 +2154,45 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F12" s="3">
         <v>-52.34375</v>
       </c>
     </row>
-    <row r="13" spans="4:6">
+    <row r="13" spans="1:6">
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="4:6">
+    <row r="15" spans="1:6">
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B16" s="2"/>
       <c r="D16" s="3"/>
@@ -1842,7 +2201,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B17" s="3">
         <v>100</v>
@@ -1853,7 +2212,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B18" s="3">
         <v>10</v>
@@ -1862,14 +2221,14 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="4:6">
+    <row r="19" spans="1:6">
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B20" s="2"/>
       <c r="D20" s="3"/>
@@ -1878,10 +2237,10 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -1908,7 +2267,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="4:6">
+    <row r="25" spans="1:6">
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>

--- a/0 zombie type/sun/sun_info.xlsx
+++ b/0 zombie type/sun/sun_info.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="18855" windowHeight="9270"/>
+    <workbookView windowWidth="16050" windowHeight="11745"/>
   </bookViews>
   <sheets>
-    <sheet name="DE 0.5 hqyx" sheetId="7" r:id="rId1"/>
-    <sheet name="NE1" sheetId="6" r:id="rId2"/>
-    <sheet name="N6E1.5 68" sheetId="5" r:id="rId3"/>
+    <sheet name="MGE 1.5 hqyx" sheetId="8" r:id="rId1"/>
+    <sheet name="DE 0.5 hqyx" sheetId="7" r:id="rId2"/>
+    <sheet name="NE1" sheetId="6" r:id="rId3"/>
+    <sheet name="N6E1.5 68" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="36">
   <si>
     <t>地图类型</t>
   </si>
@@ -61,73 +62,73 @@
     <t>密度的通常波权重和阈值线</t>
   </si>
   <si>
+    <t>橄榄</t>
+  </si>
+  <si>
+    <t>冰车</t>
+  </si>
+  <si>
+    <t>用户ID</t>
+  </si>
+  <si>
+    <t>气球</t>
+  </si>
+  <si>
+    <t>模式ID</t>
+  </si>
+  <si>
+    <t>舞王</t>
+  </si>
+  <si>
+    <t>已完成f数（偶数）</t>
+  </si>
+  <si>
+    <t>冲关选卡数</t>
+  </si>
+  <si>
+    <t>密度</t>
+  </si>
+  <si>
+    <t>阳光初值</t>
+  </si>
+  <si>
     <t>红眼</t>
   </si>
   <si>
-    <t>橄榄</t>
-  </si>
-  <si>
-    <t>用户ID</t>
-  </si>
-  <si>
-    <t>冰车</t>
-  </si>
-  <si>
-    <t>模式ID</t>
-  </si>
-  <si>
-    <t>气球</t>
-  </si>
-  <si>
-    <t>已完成f数（偶数）</t>
-  </si>
-  <si>
-    <t>舞王</t>
-  </si>
-  <si>
-    <t>冲关选卡数</t>
+    <t>破阵阳光值</t>
+  </si>
+  <si>
+    <t>阳光无上限</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>计算模式</t>
+  </si>
+  <si>
+    <t>1-随机种子模拟</t>
+  </si>
+  <si>
+    <t>模式1</t>
+  </si>
+  <si>
+    <t>模拟次数</t>
+  </si>
+  <si>
+    <t>输出种子数</t>
+  </si>
+  <si>
+    <t>模式2</t>
+  </si>
+  <si>
+    <t>种子</t>
+  </si>
+  <si>
+    <t>6A25E7B6</t>
   </si>
   <si>
     <t>白眼</t>
-  </si>
-  <si>
-    <t>阳光初值</t>
-  </si>
-  <si>
-    <t>密度</t>
-  </si>
-  <si>
-    <t>破阵阳光值</t>
-  </si>
-  <si>
-    <t>阳光无上限</t>
-  </si>
-  <si>
-    <t>否</t>
-  </si>
-  <si>
-    <t>计算模式</t>
-  </si>
-  <si>
-    <t>1-随机种子模拟</t>
-  </si>
-  <si>
-    <t>模式1</t>
-  </si>
-  <si>
-    <t>模拟次数</t>
-  </si>
-  <si>
-    <t>输出种子数</t>
-  </si>
-  <si>
-    <t>模式2</t>
-  </si>
-  <si>
-    <t>种子</t>
-  </si>
-  <si>
-    <t>6A25E7B6</t>
   </si>
   <si>
     <t>NE</t>
@@ -1339,7 +1340,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="3">
-        <v>232.452119</v>
+        <v>319.2125</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:6">
@@ -1356,7 +1357,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="3">
-        <v>-121.027542</v>
+        <v>-216.354167</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:6">
@@ -1367,7 +1368,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="3">
-        <v>-339.777542</v>
+        <v>-118.75</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:6">
@@ -1384,7 +1385,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="3">
-        <v>-323.622881</v>
+        <v>-425</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:6">
@@ -1401,7 +1402,7 @@
         <v>8</v>
       </c>
       <c r="F7" s="3">
-        <v>-439.247881</v>
+        <v>-96.041667</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:6">
@@ -1412,110 +1413,86 @@
         <v>2000</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F8" s="3">
-        <v>-241.340042</v>
+        <v>-105.416667</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:6">
       <c r="A9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="3">
+        <v>50</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="3">
-        <v>5000</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F9" s="3">
-        <v>202.409958</v>
+        <v>-93.333333</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="3">
         <v>10000</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F10" s="3">
-        <v>-113.983051</v>
+        <v>108.645833</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" s="3">
         <v>-500</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="3">
-        <v>-137.685381</v>
-      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:6">
       <c r="A12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="3">
-        <v>-134.560381</v>
-      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:6">
-      <c r="D13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="3">
-        <v>-246.027542</v>
-      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:6">
       <c r="A14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-143.220339</v>
-      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:6">
       <c r="D15" s="3" t="s">
@@ -1525,12 +1502,12 @@
         <v>8</v>
       </c>
       <c r="F15" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2"/>
       <c r="D16" s="3"/>
@@ -1539,7 +1516,7 @@
     </row>
     <row r="17" s="1" customFormat="1" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17" s="3">
         <v>10000</v>
@@ -1550,7 +1527,7 @@
     </row>
     <row r="18" s="1" customFormat="1" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18" s="3">
         <v>10</v>
@@ -1566,7 +1543,7 @@
     </row>
     <row r="20" s="1" customFormat="1" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="2"/>
       <c r="D20" s="3"/>
@@ -1575,10 +1552,10 @@
     </row>
     <row r="21" s="1" customFormat="1" spans="1:6">
       <c r="A21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -1617,21 +1594,21 @@
     <mergeCell ref="A20:B20"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1 A4:B4 A6 F15 B17 B21 B6:B10 F3:F14 F16:F25"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1 A4:B4 A6 B17 B21 B6:B10 F3:F25"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
       <formula1>"DE/MGE/AQE,NE,PE/FE,RE/ME"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3">
       <formula1>"1/-1,1/0"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8 E8 D9 E9 D10 E10 D3:E7 D11:E25">
+      <formula1>"空,路障,撑杆,铁桶,读报,铁门,橄榄,舞王,潜水,冰车,海豚,小丑,气球,矿工,跳跳,蹦极,扶梯,投篮,白眼,红眼,密度"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12">
       <formula1>"否,是"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B14">
       <formula1>"1-随机种子模拟,2-固定种子模拟"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D15:E15 D12:E14 D3:E11 D16:E25">
-      <formula1>"空,路障,撑杆,铁桶,读报,铁门,橄榄,舞王,潜水,冰车,海豚,小丑,气球,矿工,跳跳,蹦极,扶梯,投篮,白眼,红眼,密度"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1658,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -1691,7 +1668,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="3">
-        <v>43.8763</v>
+        <v>246.7</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:6">
@@ -1699,27 +1676,27 @@
         <v>9</v>
       </c>
       <c r="B4" s="3">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="3">
-        <v>-295.3125</v>
+        <v>-103.125</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:6">
       <c r="D5" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="3">
-        <v>-359.375</v>
+        <v>-321.875</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:6">
@@ -1730,13 +1707,13 @@
         <v>1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F6" s="3">
-        <v>54.6875</v>
+        <v>-246.875</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:6">
@@ -1747,13 +1724,13 @@
         <v>13</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F7" s="3">
-        <v>-76.5625</v>
+        <v>-487.5</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:6">
@@ -1764,76 +1741,82 @@
         <v>2000</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F8" s="3">
-        <v>-50</v>
+        <v>-160.9375</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F9" s="3">
-        <v>-76.5625</v>
+        <v>157.8125</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="3">
         <v>10000</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F10" s="3">
-        <v>-56.25</v>
+        <v>-182.8125</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" s="3">
         <v>-500</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F11" s="3">
-        <v>-50</v>
+        <v>-165.625</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:6">
       <c r="A12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="D12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="3">
+        <v>140.625</v>
+      </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:6">
       <c r="D13" s="3"/>
@@ -1842,23 +1825,29 @@
     </row>
     <row r="14" s="1" customFormat="1" spans="1:6">
       <c r="A14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:6">
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2"/>
       <c r="D16" s="3"/>
@@ -1867,7 +1856,7 @@
     </row>
     <row r="17" s="1" customFormat="1" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17" s="3">
         <v>10000</v>
@@ -1878,7 +1867,7 @@
     </row>
     <row r="18" s="1" customFormat="1" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18" s="3">
         <v>10</v>
@@ -1894,7 +1883,7 @@
     </row>
     <row r="20" s="1" customFormat="1" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="2"/>
       <c r="D20" s="3"/>
@@ -1903,10 +1892,10 @@
     </row>
     <row r="21" s="1" customFormat="1" spans="1:6">
       <c r="A21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -1969,6 +1958,334 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="29.6916666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.16666666666667" style="1"/>
+    <col min="4" max="5" width="7" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.69166666666667" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.16666666666667" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:6">
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3">
+        <v>43.8763</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3">
+        <v>10000</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3">
+        <v>-295.3125</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:6">
+      <c r="D5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="3">
+        <v>-359.375</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="3">
+        <v>54.6875</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3">
+        <v>13</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="3">
+        <v>-76.5625</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2000</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="3">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="3">
+        <v>5000</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="3">
+        <v>-76.5625</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="3">
+        <v>10000</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-56.25</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="3">
+        <v>-500</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="3">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:6">
+      <c r="A12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:6">
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:6">
+      <c r="A14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:6">
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:6">
+      <c r="A16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:6">
+      <c r="A17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="3">
+        <v>10000</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:6">
+      <c r="A18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="3">
+        <v>10</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:6">
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:6">
+      <c r="A20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:6">
+      <c r="A21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:6">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:6">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:6">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:6">
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A20:B20"/>
+  </mergeCells>
+  <dataValidations count="6">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1 A4:B4 A6 B17 B21 B6:B10 F3:F25"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
+      <formula1>"DE/MGE/AQE,NE,PE/FE,RE/ME"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3">
+      <formula1>"1/-1,1/0"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12">
+      <formula1>"否,是"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B14">
+      <formula1>"1-随机种子模拟,2-固定种子模拟"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:E25">
+      <formula1>"空,路障,撑杆,铁桶,读报,铁门,橄榄,舞王,潜水,冰车,海豚,小丑,气球,矿工,跳跳,蹦极,扶梯,投篮,白眼,红眼,密度"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:F25"/>
   <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.5" outlineLevelCol="5"/>
@@ -2030,7 +2347,7 @@
         <v>10500</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>8</v>
@@ -2041,7 +2358,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="D5" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>8</v>
@@ -2058,7 +2375,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>8</v>
@@ -2075,7 +2392,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>8</v>
@@ -2092,7 +2409,7 @@
         <v>2000</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>8</v>
@@ -2103,7 +2420,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="3">
         <v>500000</v>
@@ -2120,13 +2437,13 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="3">
         <v>10000</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>8</v>
@@ -2137,16 +2454,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" s="3">
         <v>-500</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F11" s="3">
         <v>60.15625</v>
@@ -2154,13 +2471,13 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>34</v>
@@ -2176,10 +2493,10 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -2192,7 +2509,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2"/>
       <c r="D16" s="3"/>
@@ -2201,7 +2518,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17" s="3">
         <v>100</v>
@@ -2212,7 +2529,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18" s="3">
         <v>10</v>
@@ -2228,7 +2545,7 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="2"/>
       <c r="D20" s="3"/>
@@ -2237,10 +2554,10 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>

--- a/0 zombie type/sun/sun_info.xlsx
+++ b/0 zombie type/sun/sun_info.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="MGE 1.5 hqyx" sheetId="8" r:id="rId1"/>
-    <sheet name="DE 0.5 hqyx" sheetId="7" r:id="rId2"/>
-    <sheet name="NE1" sheetId="6" r:id="rId3"/>
+    <sheet name="NE 1 hqyx" sheetId="6" r:id="rId2"/>
+    <sheet name="DE 0.5 hqyx" sheetId="7" r:id="rId3"/>
     <sheet name="N6E1.5 68" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="36">
   <si>
     <t>地图类型</t>
   </si>
@@ -128,10 +128,10 @@
     <t>6A25E7B6</t>
   </si>
   <si>
+    <t>NE</t>
+  </si>
+  <si>
     <t>白眼</t>
-  </si>
-  <si>
-    <t>NE</t>
   </si>
   <si>
     <t>撑杆</t>
@@ -1427,7 +1427,7 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>50</v>
+        <v>5000</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>10</v>
@@ -1502,7 +1502,7 @@
         <v>8</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:6">
@@ -1510,9 +1510,15 @@
         <v>26</v>
       </c>
       <c r="B16" s="2"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
+      <c r="D16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="3">
+        <v>170</v>
+      </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:6">
       <c r="A17" s="2" t="s">
@@ -1594,21 +1600,21 @@
     <mergeCell ref="A20:B20"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1 A4:B4 A6 B17 B21 B6:B10 F3:F25"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1 A4:B4 A6 F16 B17 B21 B6:B10 F3:F15 F17:F25"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
       <formula1>"DE/MGE/AQE,NE,PE/FE,RE/ME"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3">
       <formula1>"1/-1,1/0"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8 E8 D9 E9 D10 E10 D3:E7 D11:E25">
-      <formula1>"空,路障,撑杆,铁桶,读报,铁门,橄榄,舞王,潜水,冰车,海豚,小丑,气球,矿工,跳跳,蹦极,扶梯,投篮,白眼,红眼,密度"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12">
       <formula1>"否,是"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B14">
       <formula1>"1-随机种子模拟,2-固定种子模拟"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D16:E16 D9:E10 D3:E8 D11:E15 D17:E25">
+      <formula1>"空,路障,撑杆,铁桶,读报,铁门,橄榄,舞王,潜水,冰车,海豚,小丑,气球,矿工,跳跳,蹦极,扶梯,投篮,白眼,红眼,密度"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1635,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -1668,7 +1674,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="3">
-        <v>246.7</v>
+        <v>78.5664</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:6">
@@ -1676,7 +1682,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="3">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>20</v>
@@ -1685,7 +1691,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="3">
-        <v>-103.125</v>
+        <v>-317.5</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:6">
@@ -1696,7 +1702,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="3">
-        <v>-321.875</v>
+        <v>-331.25</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:6">
@@ -1707,13 +1713,13 @@
         <v>1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F6" s="3">
-        <v>-246.875</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:6">
@@ -1724,13 +1730,13 @@
         <v>13</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F7" s="3">
-        <v>-487.5</v>
+        <v>-85.9375</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:6">
@@ -1747,7 +1753,7 @@
         <v>8</v>
       </c>
       <c r="F8" s="3">
-        <v>-160.9375</v>
+        <v>-85.625</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:6">
@@ -1755,16 +1761,16 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>50</v>
+        <v>5000</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" s="3">
-        <v>157.8125</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:6">
@@ -1775,13 +1781,13 @@
         <v>10000</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F10" s="3">
-        <v>-182.8125</v>
+        <v>-64.0625</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:6">
@@ -1791,15 +1797,9 @@
       <c r="B11" s="3">
         <v>-500</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="3">
-        <v>-165.625</v>
-      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:6">
       <c r="A12" s="2" t="s">
@@ -1809,13 +1809,13 @@
         <v>23</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F12" s="3">
-        <v>140.625</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:6">
@@ -1835,15 +1835,9 @@
       <c r="F14" s="3"/>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:6">
-      <c r="D15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:6">
       <c r="A16" s="2" t="s">
@@ -1934,7 +1928,7 @@
     <mergeCell ref="A20:B20"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1 A4:B4 A6 B17 B21 B6:B10 F3:F25"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1 A4:B4 A6 F12 B17 B21 B6:B10 F3:F11 F13:F25"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
       <formula1>"DE/MGE/AQE,NE,PE/FE,RE/ME"</formula1>
     </dataValidation>
@@ -1944,11 +1938,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12">
       <formula1>"否,是"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D12:E12 D3:E11 D13:E25">
+      <formula1>"空,路障,撑杆,铁桶,读报,铁门,橄榄,舞王,潜水,冰车,海豚,小丑,气球,矿工,跳跳,蹦极,扶梯,投篮,白眼,红眼,密度"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B14">
       <formula1>"1-随机种子模拟,2-固定种子模拟"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:E25">
-      <formula1>"空,路障,撑杆,铁桶,读报,铁门,橄榄,舞王,潜水,冰车,海豚,小丑,气球,矿工,跳跳,蹦极,扶梯,投篮,白眼,红眼,密度"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1975,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -2008,7 +2002,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="3">
-        <v>43.8763</v>
+        <v>246.7</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:6">
@@ -2016,7 +2010,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="3">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>20</v>
@@ -2025,7 +2019,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="3">
-        <v>-295.3125</v>
+        <v>-103.125</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:6">
@@ -2036,7 +2030,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="3">
-        <v>-359.375</v>
+        <v>-321.875</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:6">
@@ -2047,13 +2041,13 @@
         <v>1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F6" s="3">
-        <v>54.6875</v>
+        <v>-246.875</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:6">
@@ -2064,13 +2058,13 @@
         <v>13</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F7" s="3">
-        <v>-76.5625</v>
+        <v>-487.5</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:6">
@@ -2081,13 +2075,13 @@
         <v>2000</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" s="3">
-        <v>-50</v>
+        <v>-160.9375</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:6">
@@ -2095,16 +2089,16 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F9" s="3">
-        <v>-76.5625</v>
+        <v>157.8125</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:6">
@@ -2115,13 +2109,13 @@
         <v>10000</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F10" s="3">
-        <v>-56.25</v>
+        <v>-182.8125</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:6">
@@ -2135,10 +2129,10 @@
         <v>10</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F11" s="3">
-        <v>-50</v>
+        <v>-165.625</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:6">
@@ -2148,9 +2142,15 @@
       <c r="B12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="D12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="3">
+        <v>140.625</v>
+      </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:6">
       <c r="D13" s="3"/>
@@ -2169,9 +2169,15 @@
       <c r="F14" s="3"/>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:6">
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:6">
       <c r="A16" s="2" t="s">
@@ -2303,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -2409,7 +2415,7 @@
         <v>2000</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>8</v>
